--- a/output/yearly_benthic_cover_iteration_15_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_15_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.94355240340045</v>
+        <v>45.06842847392814</v>
       </c>
       <c r="M2" t="n">
-        <v>100.7826206296929</v>
+        <v>100.4720976117323</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.09542706430231</v>
+        <v>87.96045638992246</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95652080225727</v>
+        <v>45.88444531731152</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228884133566612</v>
+        <v>2.22859257866331</v>
       </c>
       <c r="E3" t="n">
-        <v>5.725983577260473</v>
+        <v>5.677476035894954</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429613778555374</v>
+        <v>0.7428641928877699</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98207093218203</v>
+        <v>33.95845648848851</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17622338135472</v>
+        <v>34.17175287283742</v>
       </c>
       <c r="I3" t="n">
-        <v>6.595795050485829</v>
+        <v>6.53841301560194</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643508611597109</v>
+        <v>4.642901205548561</v>
       </c>
       <c r="K3" t="n">
-        <v>11.90457293569769</v>
+        <v>12.03954361007754</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90216735036617</v>
+        <v>48.84130103801058</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7632610883211</v>
+        <v>106.7652899653996</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.12993849887671</v>
+        <v>87.07145577445004</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63049410133987</v>
+        <v>42.62650159929576</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182158528625709</v>
+        <v>2.185827443344512</v>
       </c>
       <c r="E4" t="n">
-        <v>6.523958952952419</v>
+        <v>6.478540348910935</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445269665503366</v>
+        <v>0.744416974256379</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26968180547133</v>
+        <v>33.30681742226728</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24824046131548</v>
+        <v>34.24318081579344</v>
       </c>
       <c r="I4" t="n">
-        <v>5.508078243021842</v>
+        <v>5.460066680775149</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653293540939604</v>
+        <v>4.652606089102369</v>
       </c>
       <c r="K4" t="n">
-        <v>12.87006150112329</v>
+        <v>12.92854422554993</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31622786835668</v>
+        <v>44.2633315913876</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81678347081984</v>
+        <v>99.81837741623329</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.90276351040552</v>
+        <v>85.87545183483897</v>
       </c>
       <c r="C5" t="n">
-        <v>42.258162132215</v>
+        <v>42.2779408437201</v>
       </c>
       <c r="D5" t="n">
-        <v>2.122142240759454</v>
+        <v>2.127297583153042</v>
       </c>
       <c r="E5" t="n">
-        <v>7.110905234182466</v>
+        <v>7.064748903636433</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458554162424854</v>
+        <v>0.7457340488833952</v>
       </c>
       <c r="G5" t="n">
-        <v>32.35465992495131</v>
+        <v>32.41496140083986</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30934914715432</v>
+        <v>34.30376624863618</v>
       </c>
       <c r="I5" t="n">
-        <v>4.598255195599958</v>
+        <v>4.558105844168828</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661596351515534</v>
+        <v>4.660837805521219</v>
       </c>
       <c r="K5" t="n">
-        <v>14.09723648959445</v>
+        <v>14.12454816516104</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49159920477328</v>
+        <v>43.44584247220843</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84699782658274</v>
+        <v>99.84833148108957</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.43570665249054</v>
+        <v>84.47739551207246</v>
       </c>
       <c r="C6" t="n">
-        <v>41.50515251316514</v>
+        <v>41.5877558698808</v>
       </c>
       <c r="D6" t="n">
-        <v>2.050382794391285</v>
+        <v>2.0589031405212</v>
       </c>
       <c r="E6" t="n">
-        <v>7.510066757690304</v>
+        <v>7.471631685526833</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469854113084101</v>
+        <v>0.7468534268835956</v>
       </c>
       <c r="G6" t="n">
-        <v>31.26059919751675</v>
+        <v>31.37279257805716</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36132892018686</v>
+        <v>34.3552576366454</v>
       </c>
       <c r="I6" t="n">
-        <v>3.837684750719355</v>
+        <v>3.804123126415818</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668658820677564</v>
+        <v>4.667833918022471</v>
       </c>
       <c r="K6" t="n">
-        <v>15.56429334750946</v>
+        <v>15.52260448792753</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80282482833649</v>
+        <v>42.76302559096475</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8722706890111</v>
+        <v>99.87338594877309</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.7247241908141</v>
+        <v>82.71165431564731</v>
       </c>
       <c r="C7" t="n">
-        <v>40.39006347016355</v>
+        <v>40.41279006878805</v>
       </c>
       <c r="D7" t="n">
-        <v>1.966977321502969</v>
+        <v>1.972543148680448</v>
       </c>
       <c r="E7" t="n">
-        <v>7.738271773598153</v>
+        <v>7.68726293951696</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747949248316785</v>
+        <v>0.7478088064147029</v>
       </c>
       <c r="G7" t="n">
-        <v>29.98898051930059</v>
+        <v>30.05687146562601</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40566542257211</v>
+        <v>34.39920509507634</v>
       </c>
       <c r="I7" t="n">
-        <v>3.202197103543591</v>
+        <v>3.17415782024095</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674682801979907</v>
+        <v>4.673805040091892</v>
       </c>
       <c r="K7" t="n">
-        <v>17.2752758091859</v>
+        <v>17.28834568435269</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22805836646388</v>
+        <v>42.19319416001439</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89339764581334</v>
+        <v>99.89432991315513</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.4070148619756</v>
+        <v>87.52224124041504</v>
       </c>
       <c r="C8" t="n">
-        <v>42.6721810796281</v>
+        <v>42.70853796116325</v>
       </c>
       <c r="D8" t="n">
-        <v>1.971090634059061</v>
+        <v>1.976725597113631</v>
       </c>
       <c r="E8" t="n">
-        <v>9.548871299500373</v>
+        <v>9.512062823707527</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495133482180847</v>
+        <v>0.7493944101429671</v>
       </c>
       <c r="G8" t="n">
-        <v>30.49194120301356</v>
+        <v>30.56091145480916</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47761401803189</v>
+        <v>34.4721428665765</v>
       </c>
       <c r="I8" t="n">
-        <v>5.483525932789586</v>
+        <v>5.567289024671709</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68445842636303</v>
+        <v>4.683715063393544</v>
       </c>
       <c r="K8" t="n">
-        <v>12.59298513802442</v>
+        <v>12.47775875958495</v>
       </c>
       <c r="L8" t="n">
-        <v>44.5524310224186</v>
+        <v>44.62851962944264</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81759724007112</v>
+        <v>99.81481635019085</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.06516670463276</v>
+        <v>85.2834245529816</v>
       </c>
       <c r="C9" t="n">
-        <v>41.18116915144682</v>
+        <v>41.33351218509979</v>
       </c>
       <c r="D9" t="n">
-        <v>1.86455585898486</v>
+        <v>1.874880239116005</v>
       </c>
       <c r="E9" t="n">
-        <v>9.795734773336106</v>
+        <v>9.796619171002895</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508578561620811</v>
+        <v>0.7507557774576193</v>
       </c>
       <c r="G9" t="n">
-        <v>28.84389314195139</v>
+        <v>28.98634441708093</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53946138345573</v>
+        <v>34.5347657630505</v>
       </c>
       <c r="I9" t="n">
-        <v>4.57780208972959</v>
+        <v>4.647835576163531</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692861601013008</v>
+        <v>4.69222360911012</v>
       </c>
       <c r="K9" t="n">
-        <v>14.93483329536723</v>
+        <v>14.71657544701841</v>
       </c>
       <c r="L9" t="n">
-        <v>43.73167738838625</v>
+        <v>43.7952654505298</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8476798352003</v>
+        <v>99.84535308264799</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.38292285963166</v>
+        <v>82.8004793882979</v>
       </c>
       <c r="C10" t="n">
-        <v>39.20860363122911</v>
+        <v>39.57118715888537</v>
       </c>
       <c r="D10" t="n">
-        <v>1.743773936774544</v>
+        <v>1.763131817788181</v>
       </c>
       <c r="E10" t="n">
-        <v>9.797976876035998</v>
+        <v>9.859252458041302</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520186254613943</v>
+        <v>0.7519282205938237</v>
       </c>
       <c r="G10" t="n">
-        <v>26.97544772052509</v>
+        <v>27.25867234443663</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59285677122413</v>
+        <v>34.5886981473159</v>
       </c>
       <c r="I10" t="n">
-        <v>3.820732520476799</v>
+        <v>3.879245021410662</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700116409133715</v>
+        <v>4.699551378711397</v>
       </c>
       <c r="K10" t="n">
-        <v>17.61707714036834</v>
+        <v>17.19952061170209</v>
       </c>
       <c r="L10" t="n">
-        <v>43.04715805924339</v>
+        <v>43.10018568563023</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87283883084083</v>
+        <v>99.8708934562177</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.63599333580537</v>
+        <v>80.15009606977787</v>
       </c>
       <c r="C11" t="n">
-        <v>37.05294492948138</v>
+        <v>37.52138555309137</v>
       </c>
       <c r="D11" t="n">
-        <v>1.621574363692842</v>
+        <v>1.645157205017916</v>
       </c>
       <c r="E11" t="n">
-        <v>9.642723167600764</v>
+        <v>9.739059879668998</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530221835206969</v>
+        <v>0.7529405021469479</v>
       </c>
       <c r="G11" t="n">
-        <v>25.08507183772388</v>
+        <v>25.43474104104683</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63902044195206</v>
+        <v>34.63526309875962</v>
       </c>
       <c r="I11" t="n">
-        <v>3.188192694310772</v>
+        <v>3.23705620471914</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706388647004356</v>
+        <v>4.705878138418423</v>
       </c>
       <c r="K11" t="n">
-        <v>20.36400666419464</v>
+        <v>19.84990393022214</v>
       </c>
       <c r="L11" t="n">
-        <v>42.47691694742185</v>
+        <v>42.52095371053618</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89386854109787</v>
+        <v>99.89224319384969</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>76.93508757030278</v>
+        <v>77.40048889319874</v>
       </c>
       <c r="C12" t="n">
-        <v>34.84429032791211</v>
+        <v>35.27188259084588</v>
       </c>
       <c r="D12" t="n">
-        <v>1.502814711120892</v>
+        <v>1.52406887408448</v>
       </c>
       <c r="E12" t="n">
-        <v>9.379831453509281</v>
+        <v>9.472350939426716</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538899953964626</v>
+        <v>0.7538162307192667</v>
       </c>
       <c r="G12" t="n">
-        <v>23.24791007512291</v>
+        <v>23.56267049910065</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67893978823727</v>
+        <v>34.67554661308628</v>
       </c>
       <c r="I12" t="n">
-        <v>2.65988907568808</v>
+        <v>2.700684294785936</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711812471227891</v>
+        <v>4.711351441995416</v>
       </c>
       <c r="K12" t="n">
-        <v>23.06491242969721</v>
+        <v>22.59951110680127</v>
       </c>
       <c r="L12" t="n">
-        <v>42.00223633421538</v>
+        <v>42.03868807444399</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9114390918247</v>
+        <v>99.91008177209113</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.38441968637568</v>
+        <v>74.76840270457033</v>
       </c>
       <c r="C13" t="n">
-        <v>32.70320738951249</v>
+        <v>33.05591539564519</v>
       </c>
       <c r="D13" t="n">
-        <v>1.391887900410176</v>
+        <v>1.409407014727856</v>
       </c>
       <c r="E13" t="n">
-        <v>9.057277128689918</v>
+        <v>9.135179476678388</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546395764893135</v>
+        <v>0.7545733331985816</v>
       </c>
       <c r="G13" t="n">
-        <v>21.53191907421005</v>
+        <v>21.78995559311761</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71342051850841</v>
+        <v>34.71037332713477</v>
       </c>
       <c r="I13" t="n">
-        <v>2.218778135009614</v>
+        <v>2.252830627221992</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716497353058209</v>
+        <v>4.716083332491134</v>
       </c>
       <c r="K13" t="n">
-        <v>25.61558031362429</v>
+        <v>25.23159729542968</v>
       </c>
       <c r="L13" t="n">
-        <v>41.60732648920524</v>
+        <v>41.63746830073665</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92611419234201</v>
+        <v>99.92498099181151</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.20094357443645</v>
+        <v>82.27695048169926</v>
       </c>
       <c r="C14" t="n">
-        <v>37.64656342383185</v>
+        <v>37.75184310477088</v>
       </c>
       <c r="D14" t="n">
-        <v>1.39347547134688</v>
+        <v>1.411072268374171</v>
       </c>
       <c r="E14" t="n">
-        <v>11.76022181612471</v>
+        <v>11.72312263248721</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555003094973149</v>
+        <v>0.7554648826100649</v>
       </c>
       <c r="G14" t="n">
-        <v>23.78030505346362</v>
+        <v>23.90678817548875</v>
       </c>
       <c r="H14" t="n">
-        <v>36.97684116297383</v>
+        <v>36.84247174295123</v>
       </c>
       <c r="I14" t="n">
-        <v>2.812722826671862</v>
+        <v>2.916375263474932</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721876934358218</v>
+        <v>4.721655516312905</v>
       </c>
       <c r="K14" t="n">
-        <v>17.79905642556355</v>
+        <v>17.72304951830075</v>
       </c>
       <c r="L14" t="n">
-        <v>44.4607295398319</v>
+        <v>44.42800959188352</v>
       </c>
       <c r="M14" t="n">
-        <v>99.9063493892273</v>
+        <v>99.90290221495515</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.23923334083331</v>
+        <v>81.26845996998875</v>
       </c>
       <c r="C15" t="n">
-        <v>37.11083000279331</v>
+        <v>37.19300956717677</v>
       </c>
       <c r="D15" t="n">
-        <v>1.357634700819977</v>
+        <v>1.374023591664613</v>
       </c>
       <c r="E15" t="n">
-        <v>11.85640172049902</v>
+        <v>11.82078024215325</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756227605411024</v>
+        <v>0.7562187002356777</v>
       </c>
       <c r="G15" t="n">
-        <v>23.17629138169991</v>
+        <v>23.27909894501575</v>
       </c>
       <c r="H15" t="n">
-        <v>37.02006327799018</v>
+        <v>36.8792338813514</v>
       </c>
       <c r="I15" t="n">
-        <v>2.346192120594302</v>
+        <v>2.432737733095074</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7264225338189</v>
+        <v>4.726366876472984</v>
       </c>
       <c r="K15" t="n">
-        <v>18.76076665916668</v>
+        <v>18.73154003001125</v>
       </c>
       <c r="L15" t="n">
-        <v>44.05027214841023</v>
+        <v>43.99443997882658</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92186881037021</v>
+        <v>99.91898957601461</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.59945120879225</v>
+        <v>78.53856321617485</v>
       </c>
       <c r="C16" t="n">
-        <v>34.83263329313805</v>
+        <v>34.83810496596306</v>
       </c>
       <c r="D16" t="n">
-        <v>1.260195755864755</v>
+        <v>1.27227920621379</v>
       </c>
       <c r="E16" t="n">
-        <v>11.3315850807477</v>
+        <v>11.28364041003074</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568551640838957</v>
+        <v>0.7568699252697558</v>
       </c>
       <c r="G16" t="n">
-        <v>21.51290330032301</v>
+        <v>21.55531659485967</v>
       </c>
       <c r="H16" t="n">
-        <v>37.05078453388474</v>
+        <v>36.91099278963239</v>
       </c>
       <c r="I16" t="n">
-        <v>1.956782598363803</v>
+        <v>2.02902725723254</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730344775524348</v>
+        <v>4.730437032935972</v>
       </c>
       <c r="K16" t="n">
-        <v>21.40054879120776</v>
+        <v>21.46143678382514</v>
       </c>
       <c r="L16" t="n">
-        <v>43.70164591230433</v>
+        <v>43.63288220207028</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93482799665013</v>
+        <v>99.93242395185848</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.50668265635547</v>
+        <v>80.41329881472753</v>
       </c>
       <c r="C17" t="n">
-        <v>36.2108763060537</v>
+        <v>36.19126890293563</v>
       </c>
       <c r="D17" t="n">
-        <v>1.261207171069563</v>
+        <v>1.27334544065544</v>
       </c>
       <c r="E17" t="n">
-        <v>12.17742343028372</v>
+        <v>12.12370854188651</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574626052827963</v>
+        <v>0.7575042206180022</v>
       </c>
       <c r="G17" t="n">
-        <v>22.04384543414215</v>
+        <v>22.06704081694089</v>
       </c>
       <c r="H17" t="n">
-        <v>37.59419715037054</v>
+        <v>37.43558584644244</v>
       </c>
       <c r="I17" t="n">
-        <v>1.938405582189235</v>
+        <v>2.021712569321733</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734141283017477</v>
+        <v>4.734401378862512</v>
       </c>
       <c r="K17" t="n">
-        <v>19.49331734364452</v>
+        <v>19.58670118527248</v>
       </c>
       <c r="L17" t="n">
-        <v>44.2312446472009</v>
+        <v>44.1546959221097</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93543829689912</v>
+        <v>99.93266601031779</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.0095779181726</v>
+        <v>77.89050173912446</v>
       </c>
       <c r="C18" t="n">
-        <v>34.01205690012161</v>
+        <v>33.97959535690362</v>
       </c>
       <c r="D18" t="n">
-        <v>1.173258629509949</v>
+        <v>1.18361728783797</v>
       </c>
       <c r="E18" t="n">
-        <v>11.59765656452532</v>
+        <v>11.55038965896605</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579857902864565</v>
+        <v>0.7580507716304883</v>
       </c>
       <c r="G18" t="n">
-        <v>20.50664829415583</v>
+        <v>20.51205444212603</v>
       </c>
       <c r="H18" t="n">
-        <v>37.62016373939625</v>
+        <v>37.4625962006959</v>
       </c>
       <c r="I18" t="n">
-        <v>1.616453711008428</v>
+        <v>1.68597605517748</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737411189290354</v>
+        <v>4.73781732269055</v>
       </c>
       <c r="K18" t="n">
-        <v>21.99042208182741</v>
+        <v>22.10949826087551</v>
       </c>
       <c r="L18" t="n">
-        <v>43.94367641854571</v>
+        <v>43.85474769973973</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94615540049475</v>
+        <v>99.94384131751886</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.05618308762442</v>
+        <v>76.89632510894192</v>
       </c>
       <c r="C19" t="n">
-        <v>33.29953523758194</v>
+        <v>33.22560165379605</v>
       </c>
       <c r="D19" t="n">
-        <v>1.140020943878235</v>
+        <v>1.148166316841274</v>
       </c>
       <c r="E19" t="n">
-        <v>11.49489134964572</v>
+        <v>11.4417326754197</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584299985843023</v>
+        <v>0.7585186229510686</v>
       </c>
       <c r="G19" t="n">
-        <v>19.92570773065368</v>
+        <v>19.89769010782441</v>
       </c>
       <c r="H19" t="n">
-        <v>37.64221057604346</v>
+        <v>37.4857172445109</v>
       </c>
       <c r="I19" t="n">
-        <v>1.354734997667125</v>
+        <v>1.423758747950374</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74018749115189</v>
+        <v>4.740741393444178</v>
       </c>
       <c r="K19" t="n">
-        <v>22.94381691237557</v>
+        <v>23.10367489105808</v>
       </c>
       <c r="L19" t="n">
-        <v>43.71151646548262</v>
+        <v>43.62329410250845</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95486861544013</v>
+        <v>99.95257064736258</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.41834481603777</v>
+        <v>74.23059538507761</v>
       </c>
       <c r="C20" t="n">
-        <v>30.86936938974015</v>
+        <v>30.7781222697208</v>
       </c>
       <c r="D20" t="n">
-        <v>1.048194306533952</v>
+        <v>1.054516751543438</v>
       </c>
       <c r="E20" t="n">
-        <v>10.75725135191022</v>
+        <v>10.70634361317021</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588137120262459</v>
+        <v>0.7589229647653615</v>
       </c>
       <c r="G20" t="n">
-        <v>18.320727798104</v>
+        <v>18.27474576457347</v>
       </c>
       <c r="H20" t="n">
-        <v>37.66125494692734</v>
+        <v>37.50569967139153</v>
       </c>
       <c r="I20" t="n">
-        <v>1.129517000371957</v>
+        <v>1.187098089850086</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742585700164037</v>
+        <v>4.743268529783508</v>
       </c>
       <c r="K20" t="n">
-        <v>25.58165518396224</v>
+        <v>25.7694046149224</v>
       </c>
       <c r="L20" t="n">
-        <v>43.51134389858463</v>
+        <v>43.41292426124706</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96236847228701</v>
+        <v>99.96045114589026</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.98675728373219</v>
+        <v>80.77577970208952</v>
       </c>
       <c r="C21" t="n">
-        <v>35.03327026796933</v>
+        <v>34.91896112604486</v>
       </c>
       <c r="D21" t="n">
-        <v>1.048864810385807</v>
+        <v>1.055225228795733</v>
       </c>
       <c r="E21" t="n">
-        <v>12.96911386539769</v>
+        <v>12.91281124011284</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759299106302462</v>
+        <v>0.7594328472835798</v>
       </c>
       <c r="G21" t="n">
-        <v>20.27840239835028</v>
+        <v>20.21495211960631</v>
       </c>
       <c r="H21" t="n">
-        <v>39.63130120180803</v>
+        <v>39.45882634595743</v>
       </c>
       <c r="I21" t="n">
-        <v>1.554156487097532</v>
+        <v>1.628076624811257</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745619414390387</v>
+        <v>4.746455295522374</v>
       </c>
       <c r="K21" t="n">
-        <v>19.01324271626783</v>
+        <v>19.22422029791047</v>
       </c>
       <c r="L21" t="n">
-        <v>45.90171491685147</v>
+        <v>45.8025857915228</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94822790108861</v>
+        <v>99.94576721547813</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_15_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_15_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.06842847392814</v>
+        <v>45.09456140733436</v>
       </c>
       <c r="M2" t="n">
-        <v>100.4720976117323</v>
+        <v>99.51460350327079</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96045638992246</v>
+        <v>87.95394740264332</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88444531731152</v>
+        <v>45.8355884382789</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22859257866331</v>
+        <v>2.22861294129086</v>
       </c>
       <c r="E3" t="n">
-        <v>5.677476035894954</v>
+        <v>5.649396794354815</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428641928877699</v>
+        <v>0.7428709804302867</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95845648848851</v>
+        <v>33.94152993610324</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17175287283742</v>
+        <v>34.17206509979318</v>
       </c>
       <c r="I3" t="n">
-        <v>6.53841301560194</v>
+        <v>6.576528022981641</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642901205548561</v>
+        <v>4.642943627689291</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03954361007754</v>
+        <v>12.0460525973567</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84130103801058</v>
+        <v>48.88228286873974</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7652899653996</v>
+        <v>106.7639239043753</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.07145577445004</v>
+        <v>87.06863542065028</v>
       </c>
       <c r="C4" t="n">
-        <v>42.62650159929576</v>
+        <v>42.59050534004475</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185827443344512</v>
+        <v>2.18602016916731</v>
       </c>
       <c r="E4" t="n">
-        <v>6.478540348910935</v>
+        <v>6.456753880952743</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744416974256379</v>
+        <v>0.744432897579041</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30681742226728</v>
+        <v>33.29284670210222</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24318081579344</v>
+        <v>34.24391328863588</v>
       </c>
       <c r="I4" t="n">
-        <v>5.460066680775149</v>
+        <v>5.49196287234409</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652606089102369</v>
+        <v>4.652705609869006</v>
       </c>
       <c r="K4" t="n">
-        <v>12.92854422554993</v>
+        <v>12.93136457934971</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2633315913876</v>
+        <v>44.29544874663384</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81837741623329</v>
+        <v>99.8173186660283</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.87545183483897</v>
+        <v>85.99738738692164</v>
       </c>
       <c r="C5" t="n">
-        <v>42.2779408437201</v>
+        <v>42.37157823723157</v>
       </c>
       <c r="D5" t="n">
-        <v>2.127297583153042</v>
+        <v>2.133963679771177</v>
       </c>
       <c r="E5" t="n">
-        <v>7.064748903636433</v>
+        <v>7.067125005591947</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457340488833952</v>
+        <v>0.7457558264348093</v>
       </c>
       <c r="G5" t="n">
-        <v>32.41496140083986</v>
+        <v>32.50003209510103</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30376624863618</v>
+        <v>34.30476801600123</v>
       </c>
       <c r="I5" t="n">
-        <v>4.558105844168828</v>
+        <v>4.584768848803904</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660837805521219</v>
+        <v>4.660973915217558</v>
       </c>
       <c r="K5" t="n">
-        <v>14.12454816516104</v>
+        <v>14.00261261307835</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44584247220843</v>
+        <v>43.4732546254583</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84833148108957</v>
+        <v>99.84744547576821</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.47739551207246</v>
+        <v>84.61316524560662</v>
       </c>
       <c r="C6" t="n">
-        <v>41.5877558698808</v>
+        <v>41.69942791680671</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0589031405212</v>
+        <v>2.066239118076543</v>
       </c>
       <c r="E6" t="n">
-        <v>7.471631685526833</v>
+        <v>7.480572444849094</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468534268835956</v>
+        <v>0.7468799856474552</v>
       </c>
       <c r="G6" t="n">
-        <v>31.37279257805716</v>
+        <v>31.46859447056833</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3552576366454</v>
+        <v>34.35647933978294</v>
       </c>
       <c r="I6" t="n">
-        <v>3.804123126415818</v>
+        <v>3.826399976385674</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667833918022471</v>
+        <v>4.667999910296595</v>
       </c>
       <c r="K6" t="n">
-        <v>15.52260448792753</v>
+        <v>15.38683475439337</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76302559096475</v>
+        <v>42.78638263855537</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87338594877309</v>
+        <v>99.87264530975547</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.71165431564731</v>
+        <v>83.04407838062572</v>
       </c>
       <c r="C7" t="n">
-        <v>40.41279006878805</v>
+        <v>40.72464359532516</v>
       </c>
       <c r="D7" t="n">
-        <v>1.972543148680448</v>
+        <v>1.98973968555282</v>
       </c>
       <c r="E7" t="n">
-        <v>7.68726293951696</v>
+        <v>7.735740881185698</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478088064147029</v>
+        <v>0.7478371493698522</v>
       </c>
       <c r="G7" t="n">
-        <v>30.05687146562601</v>
+        <v>30.30351652859295</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39920509507634</v>
+        <v>34.4005088710132</v>
       </c>
       <c r="I7" t="n">
-        <v>3.17415782024095</v>
+        <v>3.192753081349625</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673805040091892</v>
+        <v>4.673982183561576</v>
       </c>
       <c r="K7" t="n">
-        <v>17.28834568435269</v>
+        <v>16.9559216193743</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19319416001439</v>
+        <v>42.21314589706759</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89432991315513</v>
+        <v>99.89371111176706</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.52224124041504</v>
+        <v>87.8865844569185</v>
       </c>
       <c r="C8" t="n">
-        <v>42.70853796116325</v>
+        <v>43.01968631411701</v>
       </c>
       <c r="D8" t="n">
-        <v>1.976725597113631</v>
+        <v>1.993978997502522</v>
       </c>
       <c r="E8" t="n">
-        <v>9.512062823707527</v>
+        <v>9.562726226024218</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493944101429671</v>
+        <v>0.7494304808929524</v>
       </c>
       <c r="G8" t="n">
-        <v>30.56091145480916</v>
+        <v>30.80520776042314</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4721428665765</v>
+        <v>34.47380212107581</v>
       </c>
       <c r="I8" t="n">
-        <v>5.567289024671709</v>
+        <v>5.617498365418909</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683715063393544</v>
+        <v>4.683940505580952</v>
       </c>
       <c r="K8" t="n">
-        <v>12.47775875958495</v>
+        <v>12.1134155430815</v>
       </c>
       <c r="L8" t="n">
-        <v>44.62851962944264</v>
+        <v>44.68004630124581</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81481635019085</v>
+        <v>99.81314815844432</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.2834245529816</v>
+        <v>85.88556553194967</v>
       </c>
       <c r="C9" t="n">
-        <v>41.33351218509979</v>
+        <v>41.89053264618219</v>
       </c>
       <c r="D9" t="n">
-        <v>1.874880239116005</v>
+        <v>1.903248786530589</v>
       </c>
       <c r="E9" t="n">
-        <v>9.796619171002895</v>
+        <v>9.909230412076775</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507557774576193</v>
+        <v>0.7507945657720805</v>
       </c>
       <c r="G9" t="n">
-        <v>28.98634441708093</v>
+        <v>29.40350643727072</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5347657630505</v>
+        <v>34.53655002551569</v>
       </c>
       <c r="I9" t="n">
-        <v>4.647835576163531</v>
+        <v>4.689769268708301</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69222360911012</v>
+        <v>4.692466036075502</v>
       </c>
       <c r="K9" t="n">
-        <v>14.71657544701841</v>
+        <v>14.11443446805032</v>
       </c>
       <c r="L9" t="n">
-        <v>43.7952654505298</v>
+        <v>43.83899126450585</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84535308264799</v>
+        <v>99.84395837873836</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.8004793882979</v>
+        <v>83.69033884630916</v>
       </c>
       <c r="C10" t="n">
-        <v>39.57118715888537</v>
+        <v>40.42291035888582</v>
       </c>
       <c r="D10" t="n">
-        <v>1.763131817788181</v>
+        <v>1.804687989040834</v>
       </c>
       <c r="E10" t="n">
-        <v>9.859252458041302</v>
+        <v>10.04844771884082</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519282205938237</v>
+        <v>0.7519650654922732</v>
       </c>
       <c r="G10" t="n">
-        <v>27.25867234443663</v>
+        <v>27.88082949458089</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5886981473159</v>
+        <v>34.59039301264456</v>
       </c>
       <c r="I10" t="n">
-        <v>3.879245021410662</v>
+        <v>3.914233906383081</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699551378711397</v>
+        <v>4.699781659326707</v>
       </c>
       <c r="K10" t="n">
-        <v>17.19952061170209</v>
+        <v>16.30966115369083</v>
       </c>
       <c r="L10" t="n">
-        <v>43.10018568563023</v>
+        <v>43.13715711884812</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8708934562177</v>
+        <v>99.86972863142476</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.15009606977787</v>
+        <v>81.44540104855096</v>
       </c>
       <c r="C11" t="n">
-        <v>37.52138555309137</v>
+        <v>38.78463606830537</v>
       </c>
       <c r="D11" t="n">
-        <v>1.645157205017916</v>
+        <v>1.705000693663039</v>
       </c>
       <c r="E11" t="n">
-        <v>9.739059879668998</v>
+        <v>10.03776222303489</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529405021469479</v>
+        <v>0.7529702725708296</v>
       </c>
       <c r="G11" t="n">
-        <v>25.43474104104683</v>
+        <v>26.34074915821126</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63526309875962</v>
+        <v>34.63663253825816</v>
       </c>
       <c r="I11" t="n">
-        <v>3.23705620471914</v>
+        <v>3.266221959245101</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705878138418423</v>
+        <v>4.706064203567685</v>
       </c>
       <c r="K11" t="n">
-        <v>19.84990393022214</v>
+        <v>18.55459895144904</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52095371053618</v>
+        <v>42.55203626062384</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89224319384969</v>
+        <v>99.89127128037825</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.40048889319874</v>
+        <v>78.90578304516517</v>
       </c>
       <c r="C12" t="n">
-        <v>35.27188259084588</v>
+        <v>36.75050628287825</v>
       </c>
       <c r="D12" t="n">
-        <v>1.52406887408448</v>
+        <v>1.593133707729878</v>
       </c>
       <c r="E12" t="n">
-        <v>9.472350939426716</v>
+        <v>9.833337665419053</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538162307192667</v>
+        <v>0.7538370584806551</v>
       </c>
       <c r="G12" t="n">
-        <v>23.56267049910065</v>
+        <v>24.61250340059816</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67554661308628</v>
+        <v>34.67650469011013</v>
       </c>
       <c r="I12" t="n">
-        <v>2.700684294785936</v>
+        <v>2.724984907323192</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711351441995416</v>
+        <v>4.711481615504094</v>
       </c>
       <c r="K12" t="n">
-        <v>22.59951110680127</v>
+        <v>21.09421695483485</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03868807444399</v>
+        <v>42.06454837453009</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91008177209113</v>
+        <v>99.90927161224319</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.76840270457033</v>
+        <v>76.40913671839559</v>
       </c>
       <c r="C13" t="n">
-        <v>33.05591539564519</v>
+        <v>34.67463563147529</v>
       </c>
       <c r="D13" t="n">
-        <v>1.409407014727856</v>
+        <v>1.484237667934225</v>
       </c>
       <c r="E13" t="n">
-        <v>9.135179476678388</v>
+        <v>9.540041434505733</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545733331985816</v>
+        <v>0.7545845809202397</v>
       </c>
       <c r="G13" t="n">
-        <v>21.78995559311761</v>
+        <v>22.93015612693377</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71037332713477</v>
+        <v>34.71089072233102</v>
       </c>
       <c r="I13" t="n">
-        <v>2.252830627221992</v>
+        <v>2.273072555019103</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716083332491134</v>
+        <v>4.716153630751498</v>
       </c>
       <c r="K13" t="n">
-        <v>25.23159729542968</v>
+        <v>23.59086328160442</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63746830073665</v>
+        <v>41.65880706171688</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92498099181151</v>
+        <v>99.9243059747966</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.27695048169926</v>
+        <v>83.12502341853582</v>
       </c>
       <c r="C14" t="n">
-        <v>37.75184310477088</v>
+        <v>38.95849356648284</v>
       </c>
       <c r="D14" t="n">
-        <v>1.411072268374171</v>
+        <v>1.485877639616869</v>
       </c>
       <c r="E14" t="n">
-        <v>11.72312263248721</v>
+        <v>11.90728436483632</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554648826100649</v>
+        <v>0.7554183404801839</v>
       </c>
       <c r="G14" t="n">
-        <v>23.90678817548875</v>
+        <v>24.85295944495953</v>
       </c>
       <c r="H14" t="n">
-        <v>36.84247174295123</v>
+        <v>36.64671087152513</v>
       </c>
       <c r="I14" t="n">
-        <v>2.916375263474932</v>
+        <v>2.755408129116636</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721655516312905</v>
+        <v>4.721364628001149</v>
       </c>
       <c r="K14" t="n">
-        <v>17.72304951830075</v>
+        <v>16.87497658146419</v>
       </c>
       <c r="L14" t="n">
-        <v>44.42800959188352</v>
+        <v>44.07478428640821</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90290221495515</v>
+        <v>99.90825443435524</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.26845996998875</v>
+        <v>82.19689877389494</v>
       </c>
       <c r="C15" t="n">
-        <v>37.19300956717677</v>
+        <v>38.45611071874048</v>
       </c>
       <c r="D15" t="n">
-        <v>1.374023591664613</v>
+        <v>1.451170897010197</v>
       </c>
       <c r="E15" t="n">
-        <v>11.82078024215325</v>
+        <v>12.01220937978164</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562187002356777</v>
+        <v>0.7561224174136836</v>
       </c>
       <c r="G15" t="n">
-        <v>23.27909894501575</v>
+        <v>24.27245049625991</v>
       </c>
       <c r="H15" t="n">
-        <v>36.8792338813514</v>
+        <v>36.68086691782508</v>
       </c>
       <c r="I15" t="n">
-        <v>2.432737733095074</v>
+        <v>2.298313556768922</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726366876472984</v>
+        <v>4.725765108835522</v>
       </c>
       <c r="K15" t="n">
-        <v>18.73154003001125</v>
+        <v>17.80310122610504</v>
       </c>
       <c r="L15" t="n">
-        <v>43.99443997882658</v>
+        <v>43.66424894045681</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91898957601461</v>
+        <v>99.92346088530232</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.53856321617485</v>
+        <v>79.59942015042986</v>
       </c>
       <c r="C16" t="n">
-        <v>34.83810496596306</v>
+        <v>36.21368478321826</v>
       </c>
       <c r="D16" t="n">
-        <v>1.27227920621379</v>
+        <v>1.352366790309666</v>
       </c>
       <c r="E16" t="n">
-        <v>11.28364041003074</v>
+        <v>11.5138151409194</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568699252697558</v>
+        <v>0.7567293457999325</v>
       </c>
       <c r="G16" t="n">
-        <v>21.55531659485967</v>
+        <v>22.61984170038562</v>
       </c>
       <c r="H16" t="n">
-        <v>36.91099278963239</v>
+        <v>36.71031011227604</v>
       </c>
       <c r="I16" t="n">
-        <v>2.02902725723254</v>
+        <v>1.916798649489633</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730437032935972</v>
+        <v>4.729558411249577</v>
       </c>
       <c r="K16" t="n">
-        <v>21.46143678382514</v>
+        <v>20.40057984957012</v>
       </c>
       <c r="L16" t="n">
-        <v>43.63288220207028</v>
+        <v>43.32189332396804</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93242395185848</v>
+        <v>99.93615795675642</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.41329881472753</v>
+        <v>81.0779812804108</v>
       </c>
       <c r="C17" t="n">
-        <v>36.19126890293563</v>
+        <v>37.31291211731963</v>
       </c>
       <c r="D17" t="n">
-        <v>1.27334544065544</v>
+        <v>1.353415283692323</v>
       </c>
       <c r="E17" t="n">
-        <v>12.12370854188651</v>
+        <v>12.21538615765641</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575042206180022</v>
+        <v>0.7573160399699012</v>
       </c>
       <c r="G17" t="n">
-        <v>22.06704081694089</v>
+        <v>23.01572343085385</v>
       </c>
       <c r="H17" t="n">
-        <v>37.43558584644244</v>
+        <v>37.11711621843456</v>
       </c>
       <c r="I17" t="n">
-        <v>2.021712569321733</v>
+        <v>1.885798899991865</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734401378862512</v>
+        <v>4.733225249811882</v>
       </c>
       <c r="K17" t="n">
-        <v>19.58670118527248</v>
+        <v>18.92201871958922</v>
       </c>
       <c r="L17" t="n">
-        <v>44.1546959221097</v>
+        <v>43.70225789749069</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93266601031779</v>
+        <v>99.93718873439953</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.89050173912446</v>
+        <v>78.58820038010157</v>
       </c>
       <c r="C18" t="n">
-        <v>33.97959535690362</v>
+        <v>35.11397652575104</v>
       </c>
       <c r="D18" t="n">
-        <v>1.18361728783797</v>
+        <v>1.262149118378144</v>
       </c>
       <c r="E18" t="n">
-        <v>11.55038965896605</v>
+        <v>11.65374538879738</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580507716304883</v>
+        <v>0.7578211689275711</v>
       </c>
       <c r="G18" t="n">
-        <v>20.51205444212603</v>
+        <v>21.46368183299699</v>
       </c>
       <c r="H18" t="n">
-        <v>37.4625962006959</v>
+        <v>37.14187329373416</v>
       </c>
       <c r="I18" t="n">
-        <v>1.68597605517748</v>
+        <v>1.572547271470003</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73781732269055</v>
+        <v>4.736382305797319</v>
       </c>
       <c r="K18" t="n">
-        <v>22.10949826087551</v>
+        <v>21.41179961989842</v>
       </c>
       <c r="L18" t="n">
-        <v>43.85474769973973</v>
+        <v>43.421840551573</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94384131751886</v>
+        <v>99.94761669722246</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.89632510894192</v>
+        <v>77.49152928959566</v>
       </c>
       <c r="C19" t="n">
-        <v>33.22560165379605</v>
+        <v>34.24270975922333</v>
       </c>
       <c r="D19" t="n">
-        <v>1.148166316841274</v>
+        <v>1.221884766174547</v>
       </c>
       <c r="E19" t="n">
-        <v>11.4417326754197</v>
+        <v>11.5031592267381</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585186229510686</v>
+        <v>0.7582537803248819</v>
       </c>
       <c r="G19" t="n">
-        <v>19.89769010782441</v>
+        <v>20.77895985179379</v>
       </c>
       <c r="H19" t="n">
-        <v>37.4857172445109</v>
+        <v>37.16307618217694</v>
       </c>
       <c r="I19" t="n">
-        <v>1.423758747950374</v>
+        <v>1.327109355356876</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740741393444178</v>
+        <v>4.739086127030511</v>
       </c>
       <c r="K19" t="n">
-        <v>23.10367489105808</v>
+        <v>22.50847071040437</v>
       </c>
       <c r="L19" t="n">
-        <v>43.62329410250845</v>
+        <v>43.20460779066775</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95257064736258</v>
+        <v>99.95578826029545</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.23059538507761</v>
+        <v>74.9162087118154</v>
       </c>
       <c r="C20" t="n">
-        <v>30.7781222697208</v>
+        <v>31.87125779105065</v>
       </c>
       <c r="D20" t="n">
-        <v>1.054516751543438</v>
+        <v>1.128518617539928</v>
       </c>
       <c r="E20" t="n">
-        <v>10.70634361317021</v>
+        <v>10.80859611377871</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589229647653615</v>
+        <v>0.7586270792675844</v>
       </c>
       <c r="G20" t="n">
-        <v>18.27474576457347</v>
+        <v>19.1912066464983</v>
       </c>
       <c r="H20" t="n">
-        <v>37.50569967139153</v>
+        <v>37.18137208442808</v>
       </c>
       <c r="I20" t="n">
-        <v>1.187098089850086</v>
+        <v>1.106468924880387</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743268529783508</v>
+        <v>4.741419245422402</v>
       </c>
       <c r="K20" t="n">
-        <v>25.7694046149224</v>
+        <v>25.0837912881846</v>
       </c>
       <c r="L20" t="n">
-        <v>43.41292426124706</v>
+        <v>43.00808677200484</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96045114589026</v>
+        <v>99.9631358512401</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.77577970208952</v>
+        <v>80.79709344474873</v>
       </c>
       <c r="C21" t="n">
-        <v>34.91896112604486</v>
+        <v>35.61974166857719</v>
       </c>
       <c r="D21" t="n">
-        <v>1.055225228795733</v>
+        <v>1.129199341043059</v>
       </c>
       <c r="E21" t="n">
-        <v>12.91281124011284</v>
+        <v>12.80448049616097</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594328472835798</v>
+        <v>0.7590846838431251</v>
       </c>
       <c r="G21" t="n">
-        <v>20.21495211960631</v>
+        <v>20.9484630095729</v>
       </c>
       <c r="H21" t="n">
-        <v>39.45882634595743</v>
+        <v>38.94948013240045</v>
       </c>
       <c r="I21" t="n">
-        <v>1.628076624811257</v>
+        <v>1.462106507708691</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746455295522374</v>
+        <v>4.744279274019531</v>
       </c>
       <c r="K21" t="n">
-        <v>19.22422029791047</v>
+        <v>19.20290655525127</v>
       </c>
       <c r="L21" t="n">
-        <v>45.8025857915228</v>
+        <v>45.12864427299346</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94576721547813</v>
+        <v>99.95129249682194</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_15_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_15_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.09456140733436</v>
+        <v>43.87623590220399</v>
       </c>
       <c r="M2" t="n">
-        <v>99.51460350327079</v>
+        <v>94.94725663094158</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.95394740264332</v>
+        <v>81.47476993626172</v>
       </c>
       <c r="C3" t="n">
-        <v>45.8355884382789</v>
+        <v>43.23032549181727</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22861294129086</v>
+        <v>2.180339879385529</v>
       </c>
       <c r="E3" t="n">
-        <v>5.649396794354815</v>
+        <v>4.146143878470899</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428709804302867</v>
+        <v>0.7376314744728236</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94152993610324</v>
+        <v>32.79594568575733</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17206509979318</v>
+        <v>33.93104782574989</v>
       </c>
       <c r="I3" t="n">
-        <v>6.576528022981641</v>
+        <v>3.073464476970099</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642943627689291</v>
+        <v>4.610196715455148</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0460525973567</v>
+        <v>18.52523006373828</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88228286873974</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7639239043753</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.06863542065028</v>
+        <v>88.60944699032339</v>
       </c>
       <c r="C4" t="n">
-        <v>42.59050534004475</v>
+        <v>42.85644621167715</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18602016916731</v>
+        <v>2.186079262601424</v>
       </c>
       <c r="E4" t="n">
-        <v>6.456753880952743</v>
+        <v>6.548655897297936</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744432897579041</v>
+        <v>0.7395731670245823</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29284670210222</v>
+        <v>33.49495037348754</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24391328863588</v>
+        <v>34.02036568313078</v>
       </c>
       <c r="I4" t="n">
-        <v>5.49196287234409</v>
+        <v>6.997490312877484</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652705609869006</v>
+        <v>4.622332293903639</v>
       </c>
       <c r="K4" t="n">
-        <v>12.93136457934971</v>
+        <v>11.3905530096766</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29544874663384</v>
+        <v>45.52036348066428</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8173186660283</v>
+        <v>99.76736270201803</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.99738738692164</v>
+        <v>87.49834382843216</v>
       </c>
       <c r="C5" t="n">
-        <v>42.37157823723157</v>
+        <v>42.83002919308655</v>
       </c>
       <c r="D5" t="n">
-        <v>2.133963679771177</v>
+        <v>2.133300497346287</v>
       </c>
       <c r="E5" t="n">
-        <v>7.067125005591947</v>
+        <v>7.364588385367826</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457558264348093</v>
+        <v>0.741219762669856</v>
       </c>
       <c r="G5" t="n">
-        <v>32.50003209510103</v>
+        <v>32.68627790070122</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30476801600123</v>
+        <v>34.09610908281337</v>
       </c>
       <c r="I5" t="n">
-        <v>4.584768848803904</v>
+        <v>5.844224682846995</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660973915217558</v>
+        <v>4.6326235166866</v>
       </c>
       <c r="K5" t="n">
-        <v>14.00261261307835</v>
+        <v>12.50165617156784</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4732546254583</v>
+        <v>44.47393990443233</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84744547576821</v>
+        <v>99.80562526908673</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.61316524560662</v>
+        <v>86.24132368357908</v>
       </c>
       <c r="C6" t="n">
-        <v>41.69942791680671</v>
+        <v>42.48006427384977</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066239118076543</v>
+        <v>2.073634966817044</v>
       </c>
       <c r="E6" t="n">
-        <v>7.480572444849094</v>
+        <v>7.971839489686427</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468799856474552</v>
+        <v>0.7426176567336127</v>
       </c>
       <c r="G6" t="n">
-        <v>31.46859447056833</v>
+        <v>31.77208690210652</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35647933978294</v>
+        <v>34.16041220974618</v>
       </c>
       <c r="I6" t="n">
-        <v>3.826399976385674</v>
+        <v>4.879372103904235</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667999910296595</v>
+        <v>4.641360354585079</v>
       </c>
       <c r="K6" t="n">
-        <v>15.38683475439337</v>
+        <v>13.7586763164209</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78638263855537</v>
+        <v>43.5989198352058</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87264530975547</v>
+        <v>99.83766042547647</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.04407838062572</v>
+        <v>84.80752754340443</v>
       </c>
       <c r="C7" t="n">
-        <v>40.72464359532516</v>
+        <v>41.80407344515564</v>
       </c>
       <c r="D7" t="n">
-        <v>1.98973968555282</v>
+        <v>2.00574191949514</v>
       </c>
       <c r="E7" t="n">
-        <v>7.735740881185698</v>
+        <v>8.389608237698727</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478371493698522</v>
+        <v>0.7438063969214019</v>
       </c>
       <c r="G7" t="n">
-        <v>30.30351652859295</v>
+        <v>30.731834478667</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4005088710132</v>
+        <v>34.21509425838448</v>
       </c>
       <c r="I7" t="n">
-        <v>3.192753081349625</v>
+        <v>4.07265227147893</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673982183561576</v>
+        <v>4.648789980758762</v>
       </c>
       <c r="K7" t="n">
-        <v>16.9559216193743</v>
+        <v>15.19247245659557</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21314589706759</v>
+        <v>42.86791598425145</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89371111176706</v>
+        <v>99.86446188600266</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.8865844569185</v>
+        <v>83.18384811233207</v>
       </c>
       <c r="C8" t="n">
-        <v>43.01968631411701</v>
+        <v>40.8129577505264</v>
       </c>
       <c r="D8" t="n">
-        <v>1.993978997502522</v>
+        <v>1.929179958683389</v>
       </c>
       <c r="E8" t="n">
-        <v>9.562726226024218</v>
+        <v>8.635781683711992</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494304808929524</v>
+        <v>0.7448193440333162</v>
       </c>
       <c r="G8" t="n">
-        <v>30.80520776042314</v>
+        <v>29.55875758170452</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47380212107581</v>
+        <v>34.26168982553254</v>
       </c>
       <c r="I8" t="n">
-        <v>5.617498365418909</v>
+        <v>3.398498818458076</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683940505580952</v>
+        <v>4.655120900208226</v>
       </c>
       <c r="K8" t="n">
-        <v>12.1134155430815</v>
+        <v>16.81615188766795</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68004630124581</v>
+        <v>42.25776113204235</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81314815844432</v>
+        <v>99.8868707702367</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.88556553194967</v>
+        <v>81.31045423635423</v>
       </c>
       <c r="C9" t="n">
-        <v>41.89053264618219</v>
+        <v>39.46715841694122</v>
       </c>
       <c r="D9" t="n">
-        <v>1.903248786530589</v>
+        <v>1.841243421807866</v>
       </c>
       <c r="E9" t="n">
-        <v>9.909230412076775</v>
+        <v>8.714704923797127</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507945657720805</v>
+        <v>0.7456850964219484</v>
       </c>
       <c r="G9" t="n">
-        <v>29.40350643727072</v>
+        <v>28.21140024244823</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53655002551569</v>
+        <v>34.30151443540962</v>
       </c>
       <c r="I9" t="n">
-        <v>4.689769268708301</v>
+        <v>2.835374263832259</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692466036075502</v>
+        <v>4.660531852637178</v>
       </c>
       <c r="K9" t="n">
-        <v>14.11443446805032</v>
+        <v>18.68954576364579</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83899126450585</v>
+        <v>41.74889307445582</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84395837873836</v>
+        <v>99.90559725504284</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.69033884630916</v>
+        <v>86.07251473351897</v>
       </c>
       <c r="C10" t="n">
-        <v>40.42291035888582</v>
+        <v>42.67547936668709</v>
       </c>
       <c r="D10" t="n">
-        <v>1.804687989040834</v>
+        <v>1.84338792047761</v>
       </c>
       <c r="E10" t="n">
-        <v>10.04844771884082</v>
+        <v>10.5585413775506</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519650654922732</v>
+        <v>0.7465535968485538</v>
       </c>
       <c r="G10" t="n">
-        <v>27.88082949458089</v>
+        <v>29.57670065956117</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59039301264456</v>
+        <v>35.67390801664778</v>
       </c>
       <c r="I10" t="n">
-        <v>3.914233906383081</v>
+        <v>3.007463182129809</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699781659326707</v>
+        <v>4.665959980303461</v>
       </c>
       <c r="K10" t="n">
-        <v>16.30966115369083</v>
+        <v>13.92748526648104</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13715711884812</v>
+        <v>43.2969032181414</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86972863142476</v>
+        <v>99.89986785130952</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.44540104855096</v>
+        <v>85.80851295836996</v>
       </c>
       <c r="C11" t="n">
-        <v>38.78463606830537</v>
+        <v>42.78305824186381</v>
       </c>
       <c r="D11" t="n">
-        <v>1.705000693663039</v>
+        <v>1.824395956577208</v>
       </c>
       <c r="E11" t="n">
-        <v>10.03776222303489</v>
+        <v>10.92823989661484</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529702725708296</v>
+        <v>0.7472930379617836</v>
       </c>
       <c r="G11" t="n">
-        <v>26.34074915821126</v>
+        <v>29.32550481088763</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63663253825816</v>
+        <v>35.76276754416256</v>
       </c>
       <c r="I11" t="n">
-        <v>3.266221959245101</v>
+        <v>2.549730224904788</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706064203567685</v>
+        <v>4.670581487261148</v>
       </c>
       <c r="K11" t="n">
-        <v>18.55459895144904</v>
+        <v>14.19148704163005</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55203626062384</v>
+        <v>42.94054780700303</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89127128037825</v>
+        <v>99.91509309049688</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.90578304516517</v>
+        <v>84.00667212685762</v>
       </c>
       <c r="C12" t="n">
-        <v>36.75050628287825</v>
+        <v>41.37772206843257</v>
       </c>
       <c r="D12" t="n">
-        <v>1.593133707729878</v>
+        <v>1.747746464822835</v>
       </c>
       <c r="E12" t="n">
-        <v>9.833337665419053</v>
+        <v>10.82353291401046</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538370584806551</v>
+        <v>0.7479236107047484</v>
       </c>
       <c r="G12" t="n">
-        <v>24.61250340059816</v>
+        <v>28.09343398158583</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67650469011013</v>
+        <v>35.7929444965504</v>
       </c>
       <c r="I12" t="n">
-        <v>2.724984907323192</v>
+        <v>2.126568092278662</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711481615504094</v>
+        <v>4.674522566904678</v>
       </c>
       <c r="K12" t="n">
-        <v>21.09421695483485</v>
+        <v>15.99332787314239</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06454837453009</v>
+        <v>42.55812421884436</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90927161224319</v>
+        <v>99.92917416041931</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.40913671839559</v>
+        <v>85.23288482693894</v>
       </c>
       <c r="C13" t="n">
-        <v>34.67463563147529</v>
+        <v>42.39032630376647</v>
       </c>
       <c r="D13" t="n">
-        <v>1.484237667934225</v>
+        <v>1.749104660248292</v>
       </c>
       <c r="E13" t="n">
-        <v>9.540041434505733</v>
+        <v>11.48675739530546</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545845809202397</v>
+        <v>0.7485048314064328</v>
       </c>
       <c r="G13" t="n">
-        <v>22.93015612693377</v>
+        <v>28.43890146442487</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71089072233102</v>
+        <v>36.144395364377</v>
       </c>
       <c r="I13" t="n">
-        <v>2.273072555019103</v>
+        <v>1.987065914886678</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716153630751498</v>
+        <v>4.678155196290206</v>
       </c>
       <c r="K13" t="n">
-        <v>23.59086328160442</v>
+        <v>14.76711517306108</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65880706171688</v>
+        <v>42.77637442515855</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9243059747966</v>
+        <v>99.93381590198609</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.12502341853582</v>
+        <v>83.31316554857766</v>
       </c>
       <c r="C14" t="n">
-        <v>38.95849356648284</v>
+        <v>40.77953045009139</v>
       </c>
       <c r="D14" t="n">
-        <v>1.485877639616869</v>
+        <v>1.669639521057177</v>
       </c>
       <c r="E14" t="n">
-        <v>11.90728436483632</v>
+        <v>11.24105658020204</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554183404801839</v>
+        <v>0.7490010563225978</v>
       </c>
       <c r="G14" t="n">
-        <v>24.85295944495953</v>
+        <v>27.14686828043454</v>
       </c>
       <c r="H14" t="n">
-        <v>36.64671087152513</v>
+        <v>36.16835746696734</v>
       </c>
       <c r="I14" t="n">
-        <v>2.755408129116636</v>
+        <v>1.656986041577741</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721364628001149</v>
+        <v>4.681256602016237</v>
       </c>
       <c r="K14" t="n">
-        <v>16.87497658146419</v>
+        <v>16.68683445142234</v>
       </c>
       <c r="L14" t="n">
-        <v>44.07478428640821</v>
+        <v>42.47843882307277</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90825443435524</v>
+        <v>99.94480372458651</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.19689877389494</v>
+        <v>82.49452540791441</v>
       </c>
       <c r="C15" t="n">
-        <v>38.45611071874048</v>
+        <v>40.20773153464661</v>
       </c>
       <c r="D15" t="n">
-        <v>1.451170897010197</v>
+        <v>1.635937103638782</v>
       </c>
       <c r="E15" t="n">
-        <v>12.01220937978164</v>
+        <v>11.24608438344893</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561224174136836</v>
+        <v>0.7494222199417773</v>
       </c>
       <c r="G15" t="n">
-        <v>24.27245049625991</v>
+        <v>26.59889665251686</v>
       </c>
       <c r="H15" t="n">
-        <v>36.68086691782508</v>
+        <v>36.18869495007498</v>
       </c>
       <c r="I15" t="n">
-        <v>2.298313556768922</v>
+        <v>1.39160122365697</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725765108835522</v>
+        <v>4.683888874636108</v>
       </c>
       <c r="K15" t="n">
-        <v>17.80310122610504</v>
+        <v>17.50547459208558</v>
       </c>
       <c r="L15" t="n">
-        <v>43.66424894045681</v>
+        <v>42.24043323441994</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92346088530232</v>
+        <v>99.95363936115213</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.59942015042986</v>
+        <v>80.19493849034893</v>
       </c>
       <c r="C16" t="n">
-        <v>36.21368478321826</v>
+        <v>38.12403138971101</v>
       </c>
       <c r="D16" t="n">
-        <v>1.352366790309666</v>
+        <v>1.541394066740563</v>
       </c>
       <c r="E16" t="n">
-        <v>11.5138151409194</v>
+        <v>10.789528982034</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567293457999325</v>
+        <v>0.7497836308840311</v>
       </c>
       <c r="G16" t="n">
-        <v>22.61984170038562</v>
+        <v>25.06171012983373</v>
       </c>
       <c r="H16" t="n">
-        <v>36.71031011227604</v>
+        <v>36.20614704849535</v>
       </c>
       <c r="I16" t="n">
-        <v>1.916798649489633</v>
+        <v>1.160226939336063</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729558411249577</v>
+        <v>4.686147693025195</v>
       </c>
       <c r="K16" t="n">
-        <v>20.40057984957012</v>
+        <v>19.80506150965105</v>
       </c>
       <c r="L16" t="n">
-        <v>43.32189332396804</v>
+        <v>42.03225151109189</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93615795675642</v>
+        <v>99.96134441045396</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.0779812804108</v>
+        <v>84.79657651221757</v>
       </c>
       <c r="C17" t="n">
-        <v>37.31291211731963</v>
+        <v>41.10905922093512</v>
       </c>
       <c r="D17" t="n">
-        <v>1.353415283692323</v>
+        <v>1.542231263427129</v>
       </c>
       <c r="E17" t="n">
-        <v>12.21538615765641</v>
+        <v>12.39465766436599</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573160399699012</v>
+        <v>0.7501908702687944</v>
       </c>
       <c r="G17" t="n">
-        <v>23.01572343085385</v>
+        <v>26.44430750166255</v>
       </c>
       <c r="H17" t="n">
-        <v>37.11711621843456</v>
+        <v>37.5947974380847</v>
       </c>
       <c r="I17" t="n">
-        <v>1.885798899991865</v>
+        <v>1.381698835228427</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733225249811882</v>
+        <v>4.688692939179965</v>
       </c>
       <c r="K17" t="n">
-        <v>18.92201871958922</v>
+        <v>15.20342348778245</v>
       </c>
       <c r="L17" t="n">
-        <v>43.70225789749069</v>
+        <v>43.64148566517574</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93718873439953</v>
+        <v>99.9539683738933</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.58820038010157</v>
+        <v>86.37948760568284</v>
       </c>
       <c r="C18" t="n">
-        <v>35.11397652575104</v>
+        <v>41.84869783417948</v>
       </c>
       <c r="D18" t="n">
-        <v>1.262149118378144</v>
+        <v>1.543526660025967</v>
       </c>
       <c r="E18" t="n">
-        <v>11.65374538879738</v>
+        <v>13.00460127836545</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578211689275711</v>
+        <v>0.7508209928223122</v>
       </c>
       <c r="G18" t="n">
-        <v>21.46368183299699</v>
+        <v>26.58489970176342</v>
       </c>
       <c r="H18" t="n">
-        <v>37.14187329373416</v>
+        <v>37.62637517476414</v>
       </c>
       <c r="I18" t="n">
-        <v>1.572547271470003</v>
+        <v>2.176632592802107</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736382305797319</v>
+        <v>4.692631205139452</v>
       </c>
       <c r="K18" t="n">
-        <v>21.41179961989842</v>
+        <v>13.62051239431714</v>
       </c>
       <c r="L18" t="n">
-        <v>43.421840551573</v>
+        <v>44.45829624265697</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94761669722246</v>
+        <v>99.92750647115359</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.49152928959566</v>
+        <v>83.82880889527925</v>
       </c>
       <c r="C19" t="n">
-        <v>34.24270975922333</v>
+        <v>39.63548000490714</v>
       </c>
       <c r="D19" t="n">
-        <v>1.221884766174547</v>
+        <v>1.448856830274075</v>
       </c>
       <c r="E19" t="n">
-        <v>11.5031592267381</v>
+        <v>12.50951237632648</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582537803248819</v>
+        <v>0.7513629177011364</v>
       </c>
       <c r="G19" t="n">
-        <v>20.77895985179379</v>
+        <v>24.95435583497025</v>
       </c>
       <c r="H19" t="n">
-        <v>37.16307618217694</v>
+        <v>37.65353300466249</v>
       </c>
       <c r="I19" t="n">
-        <v>1.327109355356876</v>
+        <v>1.8151696957127</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739086127030511</v>
+        <v>4.696018235632103</v>
       </c>
       <c r="K19" t="n">
-        <v>22.50847071040437</v>
+        <v>16.17119110472078</v>
       </c>
       <c r="L19" t="n">
-        <v>43.20460779066775</v>
+        <v>44.13286687390535</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95578826029545</v>
+        <v>99.93953798353326</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.9162087118154</v>
+        <v>81.16045790504454</v>
       </c>
       <c r="C20" t="n">
-        <v>31.87125779105065</v>
+        <v>37.2478438712196</v>
       </c>
       <c r="D20" t="n">
-        <v>1.128518617539928</v>
+        <v>1.350343700184315</v>
       </c>
       <c r="E20" t="n">
-        <v>10.80859611377871</v>
+        <v>11.91120802374116</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586270792675844</v>
+        <v>0.7518299962174645</v>
       </c>
       <c r="G20" t="n">
-        <v>19.1912066464983</v>
+        <v>23.25761696380687</v>
       </c>
       <c r="H20" t="n">
-        <v>37.18137208442808</v>
+        <v>37.6769400106725</v>
       </c>
       <c r="I20" t="n">
-        <v>1.106468924880387</v>
+        <v>1.513581734063078</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741419245422402</v>
+        <v>4.698937476359154</v>
       </c>
       <c r="K20" t="n">
-        <v>25.0837912881846</v>
+        <v>18.83954209495544</v>
       </c>
       <c r="L20" t="n">
-        <v>43.00808677200484</v>
+        <v>43.86219265338851</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9631358512401</v>
+        <v>99.94957861956357</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.79709344474873</v>
+        <v>78.56275347960749</v>
       </c>
       <c r="C21" t="n">
-        <v>35.61974166857719</v>
+        <v>34.88351394379929</v>
       </c>
       <c r="D21" t="n">
-        <v>1.129199341043059</v>
+        <v>1.254961814726977</v>
       </c>
       <c r="E21" t="n">
-        <v>12.80448049616097</v>
+        <v>11.28018893287275</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590846838431251</v>
+        <v>0.7522325638104336</v>
       </c>
       <c r="G21" t="n">
-        <v>20.9484630095729</v>
+        <v>21.61480902020727</v>
       </c>
       <c r="H21" t="n">
-        <v>38.94948013240045</v>
+        <v>37.69711413930111</v>
       </c>
       <c r="I21" t="n">
-        <v>1.462106507708691</v>
+        <v>1.261993484873745</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744279274019531</v>
+        <v>4.701453523815211</v>
       </c>
       <c r="K21" t="n">
-        <v>19.20290655525127</v>
+        <v>21.4372465203925</v>
       </c>
       <c r="L21" t="n">
-        <v>45.12864427299346</v>
+        <v>43.63719559875089</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95129249682194</v>
+        <v>99.95795606294269</v>
       </c>
     </row>
   </sheetData>
